--- a/Capitulo999_INSTITUTO/Taller2_2026/Taller02_2026.xlsx
+++ b/Capitulo999_INSTITUTO/Taller2_2026/Taller02_2026.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45114F20-AD8A-48D9-A73B-70BF71ED2BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -72,7 +73,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -407,7 +408,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="C2:F9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -524,7 +525,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="C3:F3"/>
+  <autoFilter ref="C3:F3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="C2:F2"/>
   </mergeCells>

--- a/Capitulo999_INSTITUTO/Taller2_2026/Taller02_2026.xlsx
+++ b/Capitulo999_INSTITUTO/Taller2_2026/Taller02_2026.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="27">
   <si>
     <t>CRUZ, Ramino Emmanuel</t>
   </si>
@@ -67,6 +67,42 @@
   </si>
   <si>
     <t>CONTROLES DE TALLER 1 - AÑO 2026</t>
+  </si>
+  <si>
+    <t>TORRES, Leandro Nicolás</t>
+  </si>
+  <si>
+    <t>22.05.2026</t>
+  </si>
+  <si>
+    <t>Desaprobado</t>
+  </si>
+  <si>
+    <t>MOYA, Ricardo Ignacio</t>
+  </si>
+  <si>
+    <t>T3 Y T4</t>
+  </si>
+  <si>
+    <t>BAZAN, Joaquín Carlos</t>
+  </si>
+  <si>
+    <t>ROBLEDO FERNANDEZ, Rodrigo Miguel</t>
+  </si>
+  <si>
+    <t>ONTIVERO, Maximiliano Fabian</t>
+  </si>
+  <si>
+    <t>LEGUIZAMON, Matías Joaquín</t>
+  </si>
+  <si>
+    <t>ARRASCAETA, Facundo Martín Nicolás</t>
+  </si>
+  <si>
+    <t>Falta declarar e inicializar variables</t>
+  </si>
+  <si>
+    <t>Bien</t>
   </si>
 </sst>
 </file>
@@ -408,16 +444,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C2:F9"/>
+  <dimension ref="C2:G16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C2" s="2" t="s">
         <v>14</v>
       </c>
@@ -425,7 +461,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
@@ -439,7 +475,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>0</v>
       </c>
@@ -453,7 +489,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>8</v>
       </c>
@@ -467,7 +503,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>9</v>
       </c>
@@ -481,7 +517,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>10</v>
       </c>
@@ -495,7 +531,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>12</v>
       </c>
@@ -509,7 +545,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>13</v>
       </c>
@@ -521,6 +557,107 @@
       </c>
       <c r="F9" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Capitulo999_INSTITUTO/Taller2_2026/Taller02_2026.xlsx
+++ b/Capitulo999_INSTITUTO/Taller2_2026/Taller02_2026.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$C$3:$F$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$C$3:$G$3</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="34">
   <si>
     <t>CRUZ, Ramino Emmanuel</t>
   </si>
@@ -103,6 +103,27 @@
   </si>
   <si>
     <t>Bien</t>
+  </si>
+  <si>
+    <t>05.06.2026</t>
+  </si>
+  <si>
+    <t>T4</t>
+  </si>
+  <si>
+    <t>23 al 28</t>
+  </si>
+  <si>
+    <t>23 al 29</t>
+  </si>
+  <si>
+    <t>hasta operadores ternarios</t>
+  </si>
+  <si>
+    <t>ALLENDES, Analía Mailín</t>
+  </si>
+  <si>
+    <t>hizo sus trabajos</t>
   </si>
 </sst>
 </file>
@@ -444,24 +465,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C2:G16"/>
+  <dimension ref="C2:H24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="35.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.5703125" customWidth="1"/>
+    <col min="6" max="6" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="32.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
@@ -471,11 +495,12 @@
       <c r="E3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="1"/>
+      <c r="G3" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>0</v>
       </c>
@@ -485,11 +510,11 @@
       <c r="E4" t="s">
         <v>5</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>8</v>
       </c>
@@ -499,11 +524,11 @@
       <c r="E5" t="s">
         <v>5</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>9</v>
       </c>
@@ -513,11 +538,11 @@
       <c r="E6" t="s">
         <v>5</v>
       </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>10</v>
       </c>
@@ -527,11 +552,11 @@
       <c r="E7" t="s">
         <v>5</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>12</v>
       </c>
@@ -541,11 +566,11 @@
       <c r="E8" t="s">
         <v>5</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>13</v>
       </c>
@@ -555,11 +580,11 @@
       <c r="E9" t="s">
         <v>5</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
         <v>15</v>
       </c>
@@ -569,11 +594,11 @@
       <c r="E10" t="s">
         <v>5</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>18</v>
       </c>
@@ -583,11 +608,11 @@
       <c r="E11" t="s">
         <v>19</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
         <v>20</v>
       </c>
@@ -597,11 +622,11 @@
       <c r="E12" t="s">
         <v>5</v>
       </c>
-      <c r="F12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>21</v>
       </c>
@@ -611,11 +636,11 @@
       <c r="E13" t="s">
         <v>5</v>
       </c>
-      <c r="F13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>22</v>
       </c>
@@ -625,11 +650,11 @@
       <c r="E14" t="s">
         <v>5</v>
       </c>
-      <c r="F14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
         <v>23</v>
       </c>
@@ -639,11 +664,11 @@
       <c r="E15" t="s">
         <v>5</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
         <v>24</v>
       </c>
@@ -653,17 +678,147 @@
       <c r="E16" t="s">
         <v>5</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>26</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>25</v>
       </c>
     </row>
+    <row r="17" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" t="s">
+        <v>29</v>
+      </c>
+      <c r="G17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" t="s">
+        <v>30</v>
+      </c>
+      <c r="G18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" t="s">
+        <v>28</v>
+      </c>
+      <c r="F19">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20">
+        <v>26</v>
+      </c>
+      <c r="G20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21">
+        <v>27</v>
+      </c>
+      <c r="G21" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D22" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F22">
+        <v>22</v>
+      </c>
+      <c r="G22" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F23">
+        <v>22</v>
+      </c>
+      <c r="G23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" t="s">
+        <v>27</v>
+      </c>
+      <c r="H24" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="C3:F3"/>
+  <autoFilter ref="C3:G3"/>
   <mergeCells count="1">
-    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C2:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
